--- a/public/file/Telenor Bulk Delivery.xlsx
+++ b/public/file/Telenor Bulk Delivery.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FFFD900-8577-44A4-AB04-94CC3C8DB16C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F30FFA38-8431-449E-BEDD-849137E739B3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{EBD77F68-C82E-4F71-9800-F4895BB0818A}"/>
   </bookViews>
@@ -65,7 +65,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -383,7 +383,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.5546875" customWidth="1"/>
+    <col min="1" max="1" width="24.5546875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
@@ -393,5 +393,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/public/file/Telenor Bulk Delivery.xlsx
+++ b/public/file/Telenor Bulk Delivery.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F30FFA38-8431-449E-BEDD-849137E739B3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D047B54-AA3F-4F8E-8EDA-553BF0B0A178}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{EBD77F68-C82E-4F71-9800-F4895BB0818A}"/>
   </bookViews>
@@ -25,9 +25,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
     <t>Tracking Number</t>
+  </si>
+  <si>
+    <t>Received/Refused By</t>
   </si>
 </sst>
 </file>
@@ -380,15 +383,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B76606C-1432-4F7F-B1D9-C19C93975332}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.5546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
